--- a/ข้อ1.xlsx
+++ b/ข้อ1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Product_AMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364F6108-09F5-4A4B-AF7F-DEF7844987AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5ED296F-765C-472E-BDC4-303F52EEAD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{328CC3F7-C9C7-4135-8D97-6AF8CFE33698}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{328CC3F7-C9C7-4135-8D97-6AF8CFE33698}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
